--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -76,31 +76,154 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>APOLINAR</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>ANA SHECIT</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
   </si>
   <si>
     <t>JACQUELINE</t>
   </si>
   <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
+    <t>JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
+  </si>
+  <si>
+    <t>ATZIN LUCERO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>KAREN ARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -524,16 +647,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.86</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,16 +673,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +764,7 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -658,7 +787,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -740,16 +869,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.86</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -763,16 +895,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +917,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,16 +949,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -837,22 +972,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>22330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -860,22 +995,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920195</v>
+        <v>22330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -883,22 +1018,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920286</v>
+        <v>22330051920238</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -906,24 +1041,323 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920286</v>
+        <v>22330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920243</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920245</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920318</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920319</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920237</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920414</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920248</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920250</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920399</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920235</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920254</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920257</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,154 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARELLANO</t>
+    <t>MARIANO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
     <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>KAREN ARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -624,16 +483,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.77</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -741,7 +603,7 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -846,16 +708,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.77</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -917,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,16 +814,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -967,397 +832,6 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920260</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920234</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920238</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920241</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920243</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920245</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920318</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920319</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920237</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920414</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920248</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920250</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920399</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920235</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920254</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920257</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920256</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -518,7 +518,7 @@
         <v>29</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -532,10 +532,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -544,7 +544,7 @@
         <v>30</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -620,10 +620,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>35</v>
@@ -643,10 +643,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>35</v>
@@ -731,10 +731,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -743,7 +743,7 @@
         <v>29</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -757,10 +757,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -769,7 +769,7 @@
         <v>30</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
         <v>7.6</v>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -480,7 +480,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -489,10 +489,10 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>69.77</v>
+        <v>69.05</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -597,13 +597,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>69.77</v>
+        <v>69.05</v>
       </c>
       <c r="H2">
         <v>6.9</v>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -509,16 +509,16 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>6</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -535,16 +535,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>86.11</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -600,16 +600,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,16 +626,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -646,16 +652,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -711,13 +720,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>69.05</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -734,19 +743,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,19 +769,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
     <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -791,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -823,16 +868,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>22330051920232</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -842,6 +887,144 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920357</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920237</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920082</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920082</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920077</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,58 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARIANO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
     <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -765,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -868,16 +823,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920232</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -887,144 +842,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920239</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920357</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920237</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920082</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920082</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920077</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
